--- a/AC_2014/3-Karimnagar_10_29_Sircilla.xlsx
+++ b/AC_2014/3-Karimnagar_10_29_Sircilla.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,6 +50,11 @@
       <name val="Calibri"/>
       <b val="1"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="6">
@@ -84,7 +89,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -106,11 +111,33 @@
         <color rgb="00D3D3D3"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="double">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -145,6 +172,15 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -14106,202 +14142,203 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="7" t="inlineStr">
+      <c r="A238" s="18" t="inlineStr">
         <is>
           <t>TOTAL EVM VOTES</t>
         </is>
       </c>
-      <c r="B238" s="8" t="inlineStr"/>
-      <c r="C238" s="9">
+      <c r="B238" s="11" t="inlineStr"/>
+      <c r="C238" s="19">
         <f>SUM(C6:C237)</f>
         <v/>
       </c>
-      <c r="D238" s="9">
+      <c r="D238" s="19">
         <f>SUM(D6:D237)</f>
         <v/>
       </c>
-      <c r="E238" s="9">
+      <c r="E238" s="19">
         <f>SUM(E6:E237)</f>
         <v/>
       </c>
-      <c r="F238" s="9">
+      <c r="F238" s="19">
         <f>SUM(F6:F237)</f>
         <v/>
       </c>
-      <c r="G238" s="9">
+      <c r="G238" s="19">
         <f>SUM(G6:G237)</f>
         <v/>
       </c>
-      <c r="H238" s="9">
+      <c r="H238" s="19">
         <f>SUM(H6:H237)</f>
         <v/>
       </c>
-      <c r="I238" s="9">
+      <c r="I238" s="19">
         <f>SUM(I6:I237)</f>
         <v/>
       </c>
-      <c r="J238" s="9">
+      <c r="J238" s="19">
         <f>SUM(J6:J237)</f>
         <v/>
       </c>
-      <c r="K238" s="9">
+      <c r="K238" s="19">
         <f>SUM(K6:K237)</f>
         <v/>
       </c>
-      <c r="L238" s="9">
+      <c r="L238" s="19">
         <f>SUM(L6:L237)</f>
         <v/>
       </c>
-      <c r="M238" s="9">
+      <c r="M238" s="19">
         <f>SUM(M6:M237)</f>
         <v/>
       </c>
-      <c r="N238" s="9">
+      <c r="N238" s="19">
         <f>SUM(N6:N237)</f>
         <v/>
       </c>
-      <c r="O238" s="9">
+      <c r="O238" s="19">
         <f>SUM(O6:O237)</f>
         <v/>
       </c>
-      <c r="P238" s="9">
+      <c r="P238" s="19">
         <f>SUM(P6:P237)</f>
         <v/>
       </c>
-      <c r="Q238" s="9">
+      <c r="Q238" s="19">
         <f>SUM(Q6:Q237)</f>
         <v/>
       </c>
-      <c r="R238" s="9">
+      <c r="R238" s="19">
         <f>SUM(R6:R237)</f>
         <v/>
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="10" t="inlineStr">
+      <c r="A239" s="18" t="inlineStr">
         <is>
           <t>POSTAL BALLOT VOTES</t>
         </is>
       </c>
       <c r="B239" s="11" t="inlineStr"/>
-      <c r="C239" s="12" t="n">
+      <c r="C239" s="19" t="n">
         <v>21</v>
       </c>
-      <c r="D239" s="12" t="n">
+      <c r="D239" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="E239" s="12" t="n">
+      <c r="E239" s="19" t="n">
         <v>225</v>
       </c>
-      <c r="F239" s="12" t="n">
+      <c r="F239" s="19" t="n">
         <v>495</v>
       </c>
-      <c r="G239" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H239" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I239" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J239" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K239" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L239" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M239" s="12" t="n">
+      <c r="G239" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H239" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I239" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J239" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K239" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L239" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M239" s="19" t="n">
         <v>751</v>
       </c>
-      <c r="N239" s="12" t="n">
+      <c r="N239" s="19" t="n">
         <v>121</v>
       </c>
-      <c r="O239" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="P239" s="12" t="n">
+      <c r="O239" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="P239" s="19" t="n">
         <v>874</v>
       </c>
-      <c r="Q239" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R239" s="13" t="n">
+      <c r="Q239" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R239" s="19" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="14" t="inlineStr">
+      <c r="A240" s="18" t="inlineStr">
         <is>
           <t>TOTAL VOTES POLLED</t>
         </is>
       </c>
-      <c r="B240" s="15" t="inlineStr"/>
-      <c r="C240" s="16">
+      <c r="B240" s="11" t="inlineStr"/>
+      <c r="C240" s="20">
         <f>C238+C239</f>
         <v/>
       </c>
-      <c r="D240" s="16">
+      <c r="D240" s="20">
         <f>D238+D239</f>
         <v/>
       </c>
-      <c r="E240" s="16">
+      <c r="E240" s="20">
         <f>E238+E239</f>
         <v/>
       </c>
-      <c r="F240" s="16">
+      <c r="F240" s="20">
         <f>F238+F239</f>
         <v/>
       </c>
-      <c r="G240" s="16">
+      <c r="G240" s="20">
         <f>G238+G239</f>
         <v/>
       </c>
-      <c r="H240" s="16">
+      <c r="H240" s="20">
         <f>H238+H239</f>
         <v/>
       </c>
-      <c r="I240" s="16">
+      <c r="I240" s="20">
         <f>I238+I239</f>
         <v/>
       </c>
-      <c r="J240" s="16">
+      <c r="J240" s="20">
         <f>J238+J239</f>
         <v/>
       </c>
-      <c r="K240" s="16">
+      <c r="K240" s="20">
         <f>K238+K239</f>
         <v/>
       </c>
-      <c r="L240" s="16">
+      <c r="L240" s="20">
         <f>L238+L239</f>
         <v/>
       </c>
-      <c r="M240" s="16">
+      <c r="M240" s="20">
         <f>M238+M239</f>
         <v/>
       </c>
-      <c r="N240" s="16">
+      <c r="N240" s="20">
         <f>N238+N239</f>
         <v/>
       </c>
-      <c r="O240" s="16">
+      <c r="O240" s="20">
         <f>O238+O239</f>
         <v/>
       </c>
-      <c r="P240" s="16">
+      <c r="P240" s="20">
         <f>P238+P239</f>
         <v/>
       </c>
-      <c r="Q240" s="16">
+      <c r="Q240" s="20">
         <f>Q238+Q239</f>
         <v/>
       </c>
-      <c r="R240" s="17" t="n">
-        <v>0</v>
+      <c r="R240" s="20">
+        <f>R238+R239</f>
+        <v/>
       </c>
     </row>
   </sheetData>
